--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486414_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486414_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.358000000000001</v>
+        <v>8.086600000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0035</v>
+        <v>3.917</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3545</v>
+        <v>4.1695</v>
       </c>
       <c r="G2" t="n">
         <v>5.1135</v>
@@ -610,13 +610,13 @@
         <v>2.3926</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7109</v>
+        <v>-0.9824000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2139</v>
+        <v>-0.3004</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.497</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>2.6504</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.4412</v>
+        <v>7.1851</v>
       </c>
       <c r="E3" t="n">
-        <v>7.8834</v>
+        <v>7.3498</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4422</v>
+        <v>-0.1648</v>
       </c>
       <c r="G3" t="n">
         <v>7.3291</v>
@@ -688,13 +688,13 @@
         <v>2.3926</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0205</v>
+        <v>-0.2767</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8736</v>
+        <v>0.3401</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8942</v>
+        <v>-0.6168</v>
       </c>
       <c r="V3" t="n">
         <v>-2.2599</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8219</v>
+        <v>4.98</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4743</v>
+        <v>2.1701</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3476</v>
+        <v>2.8099</v>
       </c>
       <c r="G4" t="n">
         <v>2.4587</v>
@@ -766,13 +766,13 @@
         <v>2.6101</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.6373</v>
+        <v>-0.4792</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.822</v>
+        <v>-0.1262</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8154</v>
+        <v>-0.353</v>
       </c>
       <c r="V4" t="n">
         <v>0.3904</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6555</v>
+        <v>2.304</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2807</v>
+        <v>-0.324</v>
       </c>
       <c r="F5" t="n">
-        <v>2.9362</v>
+        <v>2.628</v>
       </c>
       <c r="G5" t="n">
         <v>0.6655</v>
@@ -844,13 +844,13 @@
         <v>1.5225</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4675</v>
+        <v>0.116</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.0517</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4759</v>
+        <v>0.1676</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3327</v>
+        <v>2.1371</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0583</v>
+        <v>0.3455</v>
       </c>
       <c r="F6" t="n">
-        <v>1.391</v>
+        <v>1.7917</v>
       </c>
       <c r="G6" t="n">
         <v>2.4994</v>
@@ -922,13 +922,13 @@
         <v>1.5225</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.8394</v>
+        <v>-1.035</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8904</v>
+        <v>-0.4867</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.949</v>
+        <v>-0.5483</v>
       </c>
       <c r="V6" t="n">
         <v>1.3252</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2586</v>
+        <v>1.3464</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3806</v>
+        <v>0.5609</v>
       </c>
       <c r="F7" t="n">
-        <v>0.878</v>
+        <v>0.7855</v>
       </c>
       <c r="G7" t="n">
         <v>1.9524</v>
@@ -1000,13 +1000,13 @@
         <v>0.6525</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3463</v>
+        <v>-1.2585</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.5047</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6613</v>
+        <v>-0.7538</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.979</v>
+        <v>1.0484</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7769</v>
+        <v>1.0004</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2021</v>
+        <v>0.048</v>
       </c>
       <c r="G8" t="n">
         <v>1.6795</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5822000000000001</v>
+        <v>0.6516</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.2235</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5822000000000001</v>
+        <v>0.4281</v>
       </c>
       <c r="V8" t="n">
         <v>-0.1952</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9665</v>
+        <v>0.799</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.1224</v>
+        <v>-3.3207</v>
       </c>
       <c r="F9" t="n">
-        <v>4.0889</v>
+        <v>4.1197</v>
       </c>
       <c r="G9" t="n">
         <v>-1.172</v>
@@ -1156,13 +1156,13 @@
         <v>3.2626</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4435</v>
+        <v>0.2761</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6682</v>
+        <v>0.4699</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2246</v>
+        <v>-0.1938</v>
       </c>
       <c r="V9" t="n">
         <v>1.695</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3255</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.535</v>
+        <v>-2.9568</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2095</v>
+        <v>2.3637</v>
       </c>
       <c r="G10" t="n">
         <v>2.1508</v>
@@ -1234,13 +1234,13 @@
         <v>2.1751</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2638</v>
+        <v>-0.0039</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5997</v>
+        <v>0.1779</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3359</v>
+        <v>-0.1818</v>
       </c>
       <c r="V10" t="n">
         <v>-0.5649999999999999</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9923999999999999</v>
+        <v>-0.9307</v>
       </c>
       <c r="E11" t="n">
         <v>-1.019</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0267</v>
+        <v>0.0883</v>
       </c>
       <c r="G11" t="n">
         <v>-0.5985</v>
@@ -1312,13 +1312,13 @@
         <v>0.2175</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-0.5498</v>
       </c>
       <c r="T11" t="n">
         <v>-0.274</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3374</v>
+        <v>-0.2758</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1684</v>
+        <v>-2.0112</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.1562</v>
+        <v>-2.7524</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9878</v>
+        <v>0.7412</v>
       </c>
       <c r="G12" t="n">
         <v>-1.8842</v>
@@ -1390,13 +1390,13 @@
         <v>1.7401</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5669999999999999</v>
+        <v>-0.4098</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.2812</v>
       </c>
       <c r="U12" t="n">
-        <v>0.118</v>
+        <v>-0.1286</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3698</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.7606</v>
+        <v>-3.7576</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.7733</v>
+        <v>-4.3695</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0127</v>
+        <v>0.612</v>
       </c>
       <c r="G13" t="n">
         <v>2.5843</v>
@@ -1468,13 +1468,13 @@
         <v>2.1751</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8223</v>
+        <v>-0.8193</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.822</v>
+        <v>-0.4182</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0004</v>
+        <v>-0.4011</v>
       </c>
       <c r="V13" t="n">
         <v>-2.2599</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>19.5665</v>
+        <v>20.5939</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.4261999999999988</v>
+        <v>0.6013000000000002</v>
       </c>
       <c r="F14" t="n">
-        <v>19.9928</v>
+        <v>19.9927</v>
       </c>
       <c r="G14" t="n">
         <v>22.7785</v>
@@ -1546,13 +1546,13 @@
         <v>20.6632</v>
       </c>
       <c r="S14" t="n">
-        <v>-5.7981</v>
+        <v>-4.7709</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.2592</v>
+        <v>-1.2317</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.5391</v>
+        <v>-3.5393</v>
       </c>
       <c r="V14" t="n">
         <v>0.4112</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.6512</v>
+        <v>3.7612</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1791</v>
+        <v>1.8438</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4722</v>
+        <v>1.9174</v>
       </c>
       <c r="G15" t="n">
         <v>0.5601</v>
@@ -1624,13 +1624,13 @@
         <v>1.0875</v>
       </c>
       <c r="S15" t="n">
-        <v>1.9866</v>
+        <v>1.0965</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7487</v>
+        <v>0.4134</v>
       </c>
       <c r="U15" t="n">
-        <v>1.238</v>
+        <v>0.6832</v>
       </c>
       <c r="V15" t="n">
         <v>1.017</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. FAURE RIBES</t>
+          <t>J. ARIAS GONZALEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8156</v>
+        <v>-0.1825</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8567</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0412</v>
+        <v>-0.1825</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6733</v>
+        <v>-0.1825</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6813</v>
+        <v>-0.1825</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.008</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9046</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1.8281</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0765</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2313</v>
+        <v>-0.1825</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1468</v>
+        <v>-0.1825</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.08450000000000001</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.3926</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.2626</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.5349</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.2147</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3201</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. ARIAS GONZALEZ</t>
+          <t>A. FAURE RIBES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1825</v>
+        <v>-0.5987</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>-0.3726</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1825</v>
+        <v>-0.2261</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1825</v>
+        <v>0.6733</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1825</v>
+        <v>0.6813</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>-0.008</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1.9046</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1.8281</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.0765</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1825</v>
+        <v>-1.2313</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1825</v>
+        <v>-1.1468</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-2.3926</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.1206</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>0.9854000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>0.1352</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.6704</v>
+        <v>-1.0577</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.2484</v>
+        <v>-2.9132</v>
       </c>
       <c r="F18" t="n">
-        <v>1.578</v>
+        <v>1.8554</v>
       </c>
       <c r="G18" t="n">
         <v>-1.4131</v>
@@ -1858,13 +1858,13 @@
         <v>2.6101</v>
       </c>
       <c r="S18" t="n">
-        <v>0.096</v>
+        <v>0.7087</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2019</v>
+        <v>0.1334</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2979</v>
+        <v>0.5753</v>
       </c>
       <c r="V18" t="n">
         <v>1.3867</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. LOBACO MUÑOZ</t>
+          <t>M. TOWNES VILLAR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.0284</v>
+        <v>-1.6606</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.4575</v>
+        <v>-3.0264</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4291</v>
+        <v>1.3658</v>
       </c>
       <c r="G19" t="n">
-        <v>-4.5825</v>
+        <v>0.3674</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1098</v>
+        <v>-0.067</v>
       </c>
       <c r="I19" t="n">
-        <v>-4.4727</v>
+        <v>0.4343</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.6275</v>
+        <v>1.421</v>
       </c>
       <c r="K19" t="n">
-        <v>1.1894</v>
+        <v>0.8823</v>
       </c>
       <c r="L19" t="n">
-        <v>-3.8169</v>
+        <v>0.5387</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.955</v>
+        <v>-1.0537</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2992</v>
+        <v>-0.9493</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6558</v>
+        <v>-0.1044</v>
       </c>
       <c r="P19" t="n">
+        <v>-2.3926</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-4.3501</v>
+      </c>
+      <c r="R19" t="n">
         <v>1.9576</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-1.0875</v>
-      </c>
-      <c r="R19" t="n">
-        <v>3.0451</v>
-      </c>
       <c r="S19" t="n">
-        <v>1.6443</v>
+        <v>-0.0667</v>
       </c>
       <c r="T19" t="n">
-        <v>1.0623</v>
+        <v>-0.0973</v>
       </c>
       <c r="U19" t="n">
-        <v>0.582</v>
+        <v>0.0306</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0477</v>
+        <v>0.4313</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.243</v>
+        <v>0.4313</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. COPES</t>
+          <t>D. DUSCAK</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.077</v>
+        <v>-2.0092</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9038</v>
+        <v>-0.8203</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1732</v>
+        <v>-1.1889</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.2213</v>
+        <v>-2.3964</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.1862</v>
+        <v>-2.9136</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0351</v>
+        <v>0.5172</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.4554</v>
+        <v>-1.2941</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6538</v>
+        <v>-2.2137</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.8016</v>
+        <v>0.9196</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7659</v>
+        <v>-1.1022</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5324</v>
+        <v>-0.6998</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2335</v>
+        <v>-0.4024</v>
       </c>
       <c r="P20" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R20" t="n">
-        <v>0.87</v>
+        <v>2.1751</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4043</v>
+        <v>0.7378</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5516</v>
+        <v>0.4314</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1473</v>
+        <v>0.3064</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.13</v>
+        <v>-1.4382</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.13</v>
+        <v>-2.5682</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. DUSCAK</t>
+          <t>F. COPES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2673</v>
+        <v>-2.0655</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7085</v>
+        <v>-1.0156</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5588</v>
+        <v>-1.0499</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.3964</v>
+        <v>-2.2213</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.9136</v>
+        <v>-1.1862</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5172</v>
+        <v>-1.0351</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.2941</v>
+        <v>-1.4554</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.2137</v>
+        <v>-0.6538</v>
       </c>
       <c r="L21" t="n">
-        <v>0.9196</v>
+        <v>-0.8016</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.1022</v>
+        <v>-0.7659</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6998</v>
+        <v>-0.5324</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4024</v>
+        <v>-0.2335</v>
       </c>
       <c r="P21" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.1751</v>
+        <v>0.87</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4797</v>
+        <v>0.4158</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5432</v>
+        <v>0.4398</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0635</v>
+        <v>-0.024</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.4382</v>
+        <v>-1.13</v>
       </c>
       <c r="W21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.5682</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C. HERMANSON</t>
+          <t>P. GONZALEZ LONGARELA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6018</v>
+        <v>-2.4661</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.1264</v>
+        <v>-0.3033</v>
       </c>
       <c r="F22" t="n">
-        <v>1.5246</v>
+        <v>-2.1627</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.8377</v>
+        <v>-1.8062</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.5779</v>
+        <v>0.6903</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2598</v>
+        <v>-2.4965</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6703</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0365</v>
+        <v>0.8577</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7068</v>
+        <v>-1.4136</v>
       </c>
       <c r="M22" t="n">
+        <v>-1.2504</v>
+      </c>
+      <c r="N22" t="n">
         <v>-0.1674</v>
       </c>
-      <c r="N22" t="n">
-        <v>-0.6143999999999999</v>
-      </c>
       <c r="O22" t="n">
-        <v>0.447</v>
+        <v>-1.0829</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.3926</v>
+        <v>0.87</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.2626</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0.87</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6284999999999999</v>
+        <v>-0.3999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1935</v>
+        <v>-0.3124</v>
       </c>
       <c r="U22" t="n">
-        <v>0.822</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. TOWNES VILLAR</t>
+          <t>G. PARHAM II</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6163</v>
+        <v>-2.6612</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.9205</v>
+        <v>-3.0062</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3042</v>
+        <v>0.345</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3674</v>
+        <v>-6.0155</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.067</v>
+        <v>-1.2957</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4343</v>
+        <v>-4.7198</v>
       </c>
       <c r="J23" t="n">
-        <v>1.421</v>
+        <v>-4.9132</v>
       </c>
       <c r="K23" t="n">
-        <v>0.8823</v>
+        <v>-0.5959</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5387</v>
+        <v>-4.3173</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.0537</v>
+        <v>-1.1022</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.9493</v>
+        <v>-0.6998</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1044</v>
+        <v>-0.4024</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.3926</v>
+        <v>-0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.3501</v>
+        <v>-2.1751</v>
       </c>
       <c r="R23" t="n">
-        <v>1.9576</v>
+        <v>2.1751</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0224</v>
+        <v>0.5294</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9913999999999999</v>
+        <v>0.6922</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.031</v>
+        <v>-0.1628</v>
       </c>
       <c r="V23" t="n">
-        <v>0.4313</v>
+        <v>2.8249</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>3.3899</v>
       </c>
       <c r="X23" t="n">
-        <v>0.4313</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P. GONZALEZ LONGARELA</t>
+          <t>C. HERMANSON</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.6587</v>
+        <v>-2.6865</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.5269</v>
+        <v>-3.9029</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.1319</v>
+        <v>1.2163</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.8062</v>
+        <v>-0.8377</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6903</v>
+        <v>-0.5779</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.4965</v>
+        <v>-0.2598</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-0.6703</v>
       </c>
       <c r="K24" t="n">
-        <v>0.8577</v>
+        <v>0.0365</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.4136</v>
+        <v>-0.7068</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.2504</v>
+        <v>-0.1674</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.1674</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.0829</v>
+        <v>0.447</v>
       </c>
       <c r="P24" t="n">
-        <v>0.87</v>
+        <v>-2.3926</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="R24" t="n">
         <v>0.87</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5926</v>
+        <v>0.5438</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.536</v>
+        <v>0.03</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0566</v>
+        <v>0.5137</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.695</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>G. PARHAM II</t>
+          <t>R. LOBACO MUÑOZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.4164</v>
+        <v>-2.6912</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.4532</v>
+        <v>-2.9045</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0368</v>
+        <v>0.2133</v>
       </c>
       <c r="G25" t="n">
-        <v>-6.0155</v>
+        <v>-4.5825</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.2957</v>
+        <v>-0.1098</v>
       </c>
       <c r="I25" t="n">
-        <v>-4.7198</v>
+        <v>-4.4727</v>
       </c>
       <c r="J25" t="n">
-        <v>-4.9132</v>
+        <v>-2.6275</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.5959</v>
+        <v>1.1894</v>
       </c>
       <c r="L25" t="n">
-        <v>-4.3173</v>
+        <v>-3.8169</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.1022</v>
+        <v>-1.955</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.6998</v>
+        <v>-1.2992</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.4024</v>
+        <v>-0.6558</v>
       </c>
       <c r="P25" t="n">
-        <v>-0</v>
+        <v>1.9576</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R25" t="n">
-        <v>2.1751</v>
+        <v>3.0451</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.2259</v>
+        <v>0.9815</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2452</v>
+        <v>0.6153</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4711</v>
+        <v>0.3662</v>
       </c>
       <c r="V25" t="n">
-        <v>2.8249</v>
+        <v>-1.0477</v>
       </c>
       <c r="W25" t="n">
-        <v>3.3899</v>
+        <v>0.1952</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.243</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.5143</v>
+        <v>-5.2485</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.6832</v>
+        <v>-3.5714</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.8312</v>
+        <v>-1.6771</v>
       </c>
       <c r="G26" t="n">
         <v>-4.924</v>
@@ -2482,13 +2482,13 @@
         <v>1.9576</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.1352</v>
+        <v>0.1307</v>
       </c>
       <c r="T26" t="n">
-        <v>0.0961</v>
+        <v>0.2079</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.2313</v>
+        <v>-0.0772</v>
       </c>
       <c r="V26" t="n">
         <v>-1.3252</v>
@@ -2515,19 +2515,19 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-19.5663</v>
+        <v>-19.5665</v>
       </c>
       <c r="E27" t="n">
         <v>-19.9926</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4261000000000004</v>
+        <v>0.4259999999999999</v>
       </c>
       <c r="G27" t="n">
         <v>-22.7784</v>
       </c>
       <c r="H27" t="n">
-        <v>-4.152099999999999</v>
+        <v>-4.1521</v>
       </c>
       <c r="I27" t="n">
         <v>-18.6264</v>
@@ -2536,7 +2536,7 @@
         <v>-12.6686</v>
       </c>
       <c r="K27" t="n">
-        <v>2.678700000000001</v>
+        <v>2.6787</v>
       </c>
       <c r="L27" t="n">
         <v>-15.3472</v>
@@ -2551,7 +2551,7 @@
         <v>-3.2791</v>
       </c>
       <c r="P27" t="n">
-        <v>-2.1753</v>
+        <v>-2.175299999999999</v>
       </c>
       <c r="Q27" t="n">
         <v>-20.663</v>
@@ -2563,7 +2563,7 @@
         <v>5.7982</v>
       </c>
       <c r="T27" t="n">
-        <v>3.538999999999999</v>
+        <v>3.5391</v>
       </c>
       <c r="U27" t="n">
         <v>2.2592</v>
